--- a/report_templates/Delivery Pending.xlsx
+++ b/report_templates/Delivery Pending.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git hub repositeries\GRP_SYS\report_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b68409331e52ac1/Documents/GRP/GRP_SYS/report_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6803B7EF-F8E1-4F5E-8993-897A15E537C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{6803B7EF-F8E1-4F5E-8993-897A15E537C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B357A170-CDE9-414D-A5E2-E275B485AAD2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t xml:space="preserve">           CUSTOMER</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">   CONTACT PERSON</t>
   </si>
@@ -36,15 +33,9 @@
     <t xml:space="preserve">   PHONE NUMBER</t>
   </si>
   <si>
-    <t xml:space="preserve">                                 REMARKS</t>
-  </si>
-  <si>
     <t xml:space="preserve">   LOCATION</t>
   </si>
   <si>
-    <t xml:space="preserve">     TYPE</t>
-  </si>
-  <si>
     <t>W.O.NO.</t>
   </si>
   <si>
@@ -54,23 +45,35 @@
     <t xml:space="preserve"> BRAND</t>
   </si>
   <si>
-    <t xml:space="preserve">   DEL. DATE</t>
-  </si>
-  <si>
-    <t>DEL.STATUS</t>
-  </si>
-  <si>
     <t>DEL. COMP. DATE</t>
   </si>
   <si>
     <t>SALES PERSON</t>
+  </si>
+  <si>
+    <t>REMARKS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CUSTOMER</t>
+  </si>
+  <si>
+    <t>TYPE</t>
+  </si>
+  <si>
+    <t>DELIVERY STATUS</t>
+  </si>
+  <si>
+    <t>DEL. DATE</t>
+  </si>
+  <si>
+    <t>Qty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,6 +84,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -100,12 +111,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -114,9 +140,11 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -132,6 +160,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -397,98 +429,100 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.1796875" customWidth="1"/>
     <col min="2" max="2" width="23.81640625" customWidth="1"/>
     <col min="3" max="3" width="20.81640625" customWidth="1"/>
-    <col min="4" max="4" width="8.1796875" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.81640625" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="20.1796875" customWidth="1"/>
-    <col min="11" max="12" width="16.1796875" customWidth="1"/>
-    <col min="13" max="13" width="49.81640625" customWidth="1"/>
-    <col min="14" max="14" width="12.26953125" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" customWidth="1"/>
+    <col min="5" max="5" width="8.81640625" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.54296875" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="20.1796875" customWidth="1"/>
+    <col min="12" max="13" width="16.1796875" customWidth="1"/>
+    <col min="14" max="14" width="49.81640625" customWidth="1"/>
+    <col min="15" max="15" width="12.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="L1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="1"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/report_templates/Delivery Pending.xlsx
+++ b/report_templates/Delivery Pending.xlsx
@@ -1,31 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b68409331e52ac1/Documents/GRP/GRP_SYS/report_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{6803B7EF-F8E1-4F5E-8993-897A15E537C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B357A170-CDE9-414D-A5E2-E275B485AAD2}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_14F7C8B828278997D97CD5CBEFE4C789F143B521" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF261F85-B0C2-43DD-AEC5-E977058BA1E0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t xml:space="preserve"> CUSTOMER</t>
+  </si>
+  <si>
+    <t>TANK SIZE/MATERIAL</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BRAND</t>
+  </si>
+  <si>
+    <t>TYPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   LOCATION</t>
+  </si>
+  <si>
+    <t>DEL. DATE</t>
+  </si>
+  <si>
+    <t>DELIVERY STATUS</t>
+  </si>
   <si>
     <t xml:space="preserve">   CONTACT PERSON</t>
   </si>
@@ -33,40 +52,13 @@
     <t xml:space="preserve">   PHONE NUMBER</t>
   </si>
   <si>
-    <t xml:space="preserve">   LOCATION</t>
-  </si>
-  <si>
-    <t>W.O.NO.</t>
-  </si>
-  <si>
-    <t>TANK SIZE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> BRAND</t>
-  </si>
-  <si>
-    <t>DEL. COMP. DATE</t>
-  </si>
-  <si>
     <t>SALES PERSON</t>
   </si>
   <si>
     <t>REMARKS</t>
   </si>
   <si>
-    <t xml:space="preserve"> CUSTOMER</t>
-  </si>
-  <si>
-    <t>TYPE</t>
-  </si>
-  <si>
-    <t>DELIVERY STATUS</t>
-  </si>
-  <si>
-    <t>DEL. DATE</t>
-  </si>
-  <si>
-    <t>Qty</t>
+    <t>WO NO</t>
   </si>
 </sst>
 </file>
@@ -82,19 +74,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -107,11 +97,10 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -121,17 +110,24 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -140,17 +136,21 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -201,20 +201,20 @@
         <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -244,12 +244,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -288,244 +288,246 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
                 <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O12"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.1796875" customWidth="1"/>
-    <col min="2" max="2" width="23.81640625" customWidth="1"/>
-    <col min="3" max="3" width="20.81640625" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" customWidth="1"/>
-    <col min="5" max="5" width="8.81640625" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.54296875" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="20.1796875" customWidth="1"/>
-    <col min="12" max="13" width="16.1796875" customWidth="1"/>
-    <col min="14" max="14" width="49.81640625" customWidth="1"/>
-    <col min="15" max="15" width="12.26953125" customWidth="1"/>
+    <col min="9" max="9" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.54296875" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="49.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="O2" s="2"/>
+    <row r="2" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" s="1"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A10" s="1"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
-    </row>
+    <row r="3" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>